--- a/output/graficos_dimensiones/comunal_d_env_a_2022_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2022_biobio.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:18</t>
+    <t xml:space="preserve">2026-09-10 01:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2022_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2022_biobio.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:32</t>
+    <t xml:space="preserve">2026-09-12 22:43</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2022_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2022_biobio.xlsx
@@ -36,24 +36,24 @@
     <t xml:space="preserve">Biobío</t>
   </si>
   <si>
+    <t xml:space="preserve">San Rosendo</t>
+  </si>
+  <si>
     <t xml:space="preserve">Quilaco</t>
   </si>
   <si>
-    <t xml:space="preserve">San Rosendo</t>
+    <t xml:space="preserve">Yumbel</t>
   </si>
   <si>
     <t xml:space="preserve">Florida</t>
   </si>
   <si>
-    <t xml:space="preserve">Yumbel</t>
+    <t xml:space="preserve">Antuco</t>
   </si>
   <si>
     <t xml:space="preserve">Quilleco</t>
   </si>
   <si>
-    <t xml:space="preserve">Antuco</t>
-  </si>
-  <si>
     <t xml:space="preserve">Concepción</t>
   </si>
   <si>
@@ -75,21 +75,21 @@
     <t xml:space="preserve">Hualpén</t>
   </si>
   <si>
+    <t xml:space="preserve">Chiguayante</t>
+  </si>
+  <si>
     <t xml:space="preserve">Santa Juana</t>
   </si>
   <si>
-    <t xml:space="preserve">Chiguayante</t>
-  </si>
-  <si>
     <t xml:space="preserve">Laja</t>
   </si>
   <si>
+    <t xml:space="preserve">Santa Bárbara</t>
+  </si>
+  <si>
     <t xml:space="preserve">Penco</t>
   </si>
   <si>
-    <t xml:space="preserve">Santa Bárbara</t>
-  </si>
-  <si>
     <t xml:space="preserve">Mulchén</t>
   </si>
   <si>
@@ -99,12 +99,12 @@
     <t xml:space="preserve">Negrete</t>
   </si>
   <si>
+    <t xml:space="preserve">Nacimiento</t>
+  </si>
+  <si>
     <t xml:space="preserve">Curanilahue</t>
   </si>
   <si>
-    <t xml:space="preserve">Nacimiento</t>
-  </si>
-  <si>
     <t xml:space="preserve">Arauco</t>
   </si>
   <si>
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 22:43</t>
+    <t xml:space="preserve">2026-09-24 00:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -571,13 +571,13 @@
         <v>6</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>8308</v>
+        <v>8310</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>157.14</v>
+        <v>170.33</v>
       </c>
     </row>
     <row r="3">
@@ -588,13 +588,13 @@
         <v>7</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>8310</v>
+        <v>8308</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>155.79</v>
+        <v>170.01</v>
       </c>
     </row>
     <row r="4">
@@ -605,13 +605,13 @@
         <v>8</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>8104</v>
+        <v>8313</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>151.36</v>
+        <v>164.13</v>
       </c>
     </row>
     <row r="5">
@@ -622,13 +622,13 @@
         <v>9</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>8313</v>
+        <v>8104</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>150.79</v>
+        <v>162.17</v>
       </c>
     </row>
     <row r="6">
@@ -639,13 +639,13 @@
         <v>10</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>8309</v>
+        <v>8302</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>144.09</v>
+        <v>156.21</v>
       </c>
     </row>
     <row r="7">
@@ -656,13 +656,13 @@
         <v>11</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>8302</v>
+        <v>8309</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>142.09</v>
+        <v>155.79</v>
       </c>
     </row>
     <row r="8">
@@ -679,7 +679,7 @@
         <v>2022</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>137.56</v>
+        <v>147.19</v>
       </c>
     </row>
     <row r="9">
@@ -696,7 +696,7 @@
         <v>2022</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>135.12</v>
+        <v>145.43</v>
       </c>
     </row>
     <row r="10">
@@ -713,7 +713,7 @@
         <v>2022</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>133.99</v>
+        <v>144.13</v>
       </c>
     </row>
     <row r="11">
@@ -730,7 +730,7 @@
         <v>2022</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>126.26</v>
+        <v>137.17</v>
       </c>
     </row>
     <row r="12">
@@ -747,7 +747,7 @@
         <v>2022</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>126.21</v>
+        <v>135.77</v>
       </c>
     </row>
     <row r="13">
@@ -764,7 +764,7 @@
         <v>2022</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>124.62</v>
+        <v>135.32</v>
       </c>
     </row>
     <row r="14">
@@ -781,7 +781,7 @@
         <v>2022</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>124.44</v>
+        <v>134.17</v>
       </c>
     </row>
     <row r="15">
@@ -792,13 +792,13 @@
         <v>19</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>8109</v>
+        <v>8103</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>120.11</v>
+        <v>129.26</v>
       </c>
     </row>
     <row r="16">
@@ -809,13 +809,13 @@
         <v>20</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>8103</v>
+        <v>8109</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>120.02</v>
+        <v>128.43</v>
       </c>
     </row>
     <row r="17">
@@ -832,7 +832,7 @@
         <v>2022</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>117.07</v>
+        <v>125.75</v>
       </c>
     </row>
     <row r="18">
@@ -843,13 +843,13 @@
         <v>22</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>8107</v>
+        <v>8311</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>115.51</v>
+        <v>123.67</v>
       </c>
     </row>
     <row r="19">
@@ -860,13 +860,13 @@
         <v>23</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>8311</v>
+        <v>8107</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>114.24</v>
+        <v>123.64</v>
       </c>
     </row>
     <row r="20">
@@ -883,7 +883,7 @@
         <v>2022</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>112.17</v>
+        <v>121.07</v>
       </c>
     </row>
     <row r="21">
@@ -900,7 +900,7 @@
         <v>2022</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>107.42</v>
+        <v>116.46</v>
       </c>
     </row>
     <row r="22">
@@ -917,7 +917,7 @@
         <v>2022</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>106.97</v>
+        <v>115.19</v>
       </c>
     </row>
     <row r="23">
@@ -928,13 +928,13 @@
         <v>27</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>8205</v>
+        <v>8306</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>106.44</v>
+        <v>114.97</v>
       </c>
     </row>
     <row r="24">
@@ -945,13 +945,13 @@
         <v>28</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>8306</v>
+        <v>8205</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>106.26</v>
+        <v>114.07</v>
       </c>
     </row>
     <row r="25">
@@ -968,7 +968,7 @@
         <v>2022</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>97.93</v>
+        <v>105.48</v>
       </c>
     </row>
     <row r="26">
@@ -985,7 +985,7 @@
         <v>2022</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>95.53</v>
+        <v>102.32</v>
       </c>
     </row>
     <row r="27">
@@ -1002,7 +1002,7 @@
         <v>2022</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>95.35</v>
+        <v>102.3</v>
       </c>
     </row>
     <row r="28">
@@ -1019,7 +1019,7 @@
         <v>2022</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>91.54</v>
+        <v>98.41</v>
       </c>
     </row>
     <row r="29">
@@ -1036,7 +1036,7 @@
         <v>2022</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>91.13</v>
+        <v>98.3</v>
       </c>
     </row>
     <row r="30">
@@ -1053,7 +1053,7 @@
         <v>2022</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>87.72</v>
+        <v>94.26</v>
       </c>
     </row>
     <row r="31">
@@ -1070,7 +1070,7 @@
         <v>2022</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>79.73</v>
+        <v>86.2</v>
       </c>
     </row>
     <row r="32">
@@ -1087,7 +1087,7 @@
         <v>2022</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>73.97</v>
+        <v>79.71</v>
       </c>
     </row>
     <row r="33">
@@ -1104,7 +1104,7 @@
         <v>2022</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>69.29</v>
+        <v>74.23</v>
       </c>
     </row>
     <row r="34">
@@ -1121,7 +1121,7 @@
         <v>2022</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>50.67</v>
+        <v>54.11</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_d_env_a_2022_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2022_biobio.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:12</t>
+    <t xml:space="preserve">2026-10-02 16:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2022_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2022_biobio.xlsx
@@ -114,7 +114,7 @@
     <t xml:space="preserve">Hualqui</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Angeles</t>
+    <t xml:space="preserve">Los Ángeles</t>
   </si>
   <si>
     <t xml:space="preserve">Cañete</t>
@@ -123,7 +123,7 @@
     <t xml:space="preserve">Coronel</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Alamos</t>
+    <t xml:space="preserve">Los Álamos</t>
   </si>
   <si>
     <t xml:space="preserve">San Pedro de la Paz</t>
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 16:04</t>
+    <t xml:space="preserve">2026-10-04 10:43</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2022_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2022_biobio.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 10:43</t>
+    <t xml:space="preserve">2026-10-05 16:38</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
